--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -1785,12 +1785,18 @@
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="G19" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>MarketScreener; financial details not publicly disclosed</t>
+          <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M; ~4.0x implied</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2242,7 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -1482,15 +1482,21 @@
           <t>Jan-22</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I11" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>MarketScreener; SEK 100M (~A$13.8M); EBITDA/Revenue not disclosed; described as "not material" to APM</t>
+          <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M); expected FY22 EBITDA SEK 12M (~A$2M); ~8.3x implied; Revenue ~SEK 70.6M (~A$10.6M est. from Swedish registry)</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2238,7 @@
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34">
@@ -2242,7 +2248,7 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -1398,7 +1398,9 @@
           <t>Jun-22</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n"/>
+      <c r="F9" s="3" t="n">
+        <v>60.4</v>
+      </c>
       <c r="G9" s="3" t="n">
         <v>9.5</v>
       </c>
@@ -1410,7 +1412,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (3 Jun 2022); A$45M upfront (A$70M max); expected FY23 EBITDA ~A$9.5M; 4.7x upfront</t>
+          <t>ASX Announcement (3 Jun 2022); A$45M upfront (A$70M max); expected FY23 EBITDA ~A$9.5M; 4.7x upfront; Revenue ~A$60M (est.)</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1612,7 @@
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (1 Jun 2021); A$6.7M upfront (up to A$10.5M for 100%); standalone EBITDA not separately disclosed</t>
+          <t>ASX Announcement (1 Jun 2021); A$6.7M upfront for 75% (up to A$10.5M for 100%); combined EBITDA with Techforce ~A$5.8M FY22; 14% revenue CAGR</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1685,18 @@
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>3.1</v>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Mar 2021); financial details not publicly disclosed</t>
+          <t>ASX Announcement (15 Mar 2021); A$3.1M cash; expected EBITDA A$1M in 12 months post-completion; ~3.1x implied</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1853,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Serendipity (WA) Pty Ltd</t>
+          <t>Serendipity (WA) Pty Ltd (t/a APM)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1868,13 +1876,21 @@
           <t>Jun-20</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="F21" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>10.1</v>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Transaction details not publicly available; may relate to MDP/APM Group transaction (A$1.6B EV)</t>
+          <t>ASX/media (Jun 2020); Serendipity (WA) = APM legal entity; MDP acquired 55% at ~A$1.5B EV from Quadrant PE; FY20 Revenue ~A$1.1B, EBITDA ~A$148M</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2012,7 @@
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); combined with First Choice Care above (A$16.8M total)</t>
+          <t>ASX Announcement (Jun 2019); combined with First Choice Care (A$16.8M total); EBITDA A$3.4M combined; individual split not disclosed</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2043,18 @@
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="G25" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); IT recruitment firm; standalone financial terms not publicly disclosed</t>
+          <t>ASX Announcement (Jun 2019); A$13.5M upfront (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M; ~3.5x upfront</t>
         </is>
       </c>
     </row>
@@ -2064,11 +2086,13 @@
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="H26" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Mar 2019); acquisition of remaining shares; financial terms not publicly disclosed</t>
+          <t>ASX Announcement (Mar 2019); A$2.8M for remaining 50% shares; combined EBITDA with VNS ~A$1.1M incremental</t>
         </is>
       </c>
     </row>
@@ -2100,11 +2124,13 @@
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="H27" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Mar 2019); financial terms not publicly disclosed</t>
+          <t>ASX Announcement (Mar 2019); A$2.5M cash; combined EBITDA with Recon ~A$1.1M incremental; standalone EBITDA not disclosed</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2203,18 @@
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jan 2018); financial terms not publicly disclosed</t>
+          <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months; ~3.5x stated</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2280,7 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,6 +539,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Source Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -582,6 +588,11 @@
           <t>ASX Scheme Booklet (Dec 2024); FY24 Operating EBITDA; EV includes ~$199M net debt</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://investors.sgfleet.com/DownloadFile.axd?file=/Report/ComNews/20241204/02890088.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -624,6 +635,11 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (1 Mar 2024); ~A$9M base + ~A$1M earnout; 3.8-4.0x stated range</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/acf/acrow-limited/news/acquisition-of-benchmark-scaffolding-3001857.html</t>
         </is>
       </c>
     </row>
@@ -664,6 +680,11 @@
           <t>ASX Announcement (19 Dec 2023); A$10M asset sale (contracts &amp; assets); standalone financials not disclosed</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketindex.com.au/asx/mah/announcements/macmahon-completes-pit-n-portal-acquisition-6A1192683</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -704,6 +725,11 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (6 Nov 2023); A$26.4M upfront + A$9.9M deferred; ~4.0x upfront EV/EBITDA stated</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/acf/acrow-limited/news/acquisition-of-mi-scaffold-and-equity-raising-2952231.html</t>
         </is>
       </c>
     </row>
@@ -744,6 +770,11 @@
           <t>ASX Announcement (24 Aug 2023); A$8.5M total consideration; EBITDA/Revenue not publicly disclosed</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/AVADA-GROUP-LIMITED-129389843/news/AVADA-Group-Limited-entered-in-a-binding-agreement-to-acquire-Sta-Traffic-Management-Pty-Ltd-fir-AUD-44687162/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -788,6 +819,11 @@
           <t>ASX Announcement (20 Jun 2022); A$17.6M upfront (up to A$23.5M with earnout); ~A$34M revenue, ~A$5M EBITDA</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/avd/avada-group-limited/news/avada-confirms-completion-of-construct-traffic-acquisition-2754130.html</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -832,6 +868,11 @@
           <t>ASX Announcement (20 Apr 2022); A$15M consideration; FY21 revenue ~$6.3M, EBITDA ~$3.8M</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/ssh/ssh-group-ltd/news/transformative-eps-accretive-equipment-business-acquisition-2698290.html</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -876,6 +917,11 @@
           <t>ASX Announcement (29 Jan 2020); 3.6x FY19 Operating EBITDA explicitly stated; A$62M cash + A$10M shares</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://announcements.asx.com.au/asxpdf/20200129/pdf/44dl8skrl5by12.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -918,6 +964,11 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (17 Oct 2019); A$21.25M before earnouts; 4.4x FY19 normalised EBITDA stated</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/acf/acrow-limited/news/acquisition-of-uni-span-australia-pty-ltd-2251229.html</t>
         </is>
       </c>
     </row>
@@ -960,6 +1011,11 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (30 Apr 2018); A$80M EV; ~3.3x annualised Operating EBITDA stated</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.emecogroup.com/assets/reports/uploads/2018/07/1-20180430_Emeco-to-acquire-Matilda-Equipment.pdf</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1013,7 +1069,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1073,6 +1130,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Source Link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1115,6 +1177,11 @@
           <t>ASX Announcement (20 Feb 2026); NZD 24M upfront (NZD 56M max); NZD 5M EBITDA; 4.8x stated; converted at NZD/AUD ~0.92</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/ppe/peoplein-limited/news/completion-of-acquisition-of-infrawork-holdings-3321455.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1155,6 +1222,11 @@
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (Dec 2025); A$20.25M; 6.2x FY25 earnings stated by PeopleIN</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessnewsaustralia.com/articles/peoplein-to-sell-first-choice-care-and-edmen.html</t>
         </is>
       </c>
     </row>
@@ -1195,6 +1267,11 @@
           <t>ASX Announcement (27 Nov 2025); A$23.5M for 79.3% stake (~A$29.6M implied 100%); EBITDA/Revenue not disclosed</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/ppe/peoplein-limited/news/peoplein-to-divest-techforce-personnel-3283656.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1239,6 +1316,11 @@
           <t>ASX Scheme Booklet (Aug 2024); $1.45/share; ~A$1.3B equity + ~A$800M net debt; FY24 EBITDA A$281M</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/apm/apm-human-services-international/news/scheme-booklet-registered-with-asic-3070553.html</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1283,6 +1365,11 @@
           <t>ASX Announcement (3 Feb 2023); A$14.2-15.9M; EBITDA A$4.1-5.0M expected FY23; Revenue ~A$62.8M (FY24 full year)</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/ASHLEY-SERVICES-GROUP-LIM-55288579/news/Ashley-Services-Completes-Acquisition-of-Owen-Pacific-Workforce-42906039/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1327,6 +1414,11 @@
           <t>ASX Announcement (Nov 2022); A$239.8M (US$153.5M); FY22 Revenue A$454.7M, EBITDA A$50M</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://newsnreleases.com/2022/11/02/apm-completes-acquisition-of-equus-workforce-solutions/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1371,6 +1463,11 @@
           <t>ASX Announcement (30 May 2022); A$3.6-4.2M for 75%; normalised FY22 EBITDA A$1.4M; Revenue ~A$14M</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/ash/ashley-services-group/news/ashley-acquires-major-shareholding-in-linc-personnel-2730158.html</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1413,6 +1510,11 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (3 Jun 2022); A$45M upfront (A$70M max); expected FY23 EBITDA ~A$9.5M; 4.7x upfront; Revenue ~A$60M (est.)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessnewsaustralia.com/articles/peoplein-buys-food-industry-people-for--45-million.html</t>
         </is>
       </c>
     </row>
@@ -1457,6 +1559,11 @@
           <t>ASX Announcement (9 Feb 2022); A$16M upfront (up to A$26.8M); expected FY23 EBITDA ~A$4.3M</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/Peoplein-Limited-agreed-to-acquire-Perigon-Group-Pty-Ltd-for-AUD-26-8-million-37827523/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1499,6 +1606,11 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M); expected FY22 EBITDA SEK 12M (~A$2M); ~8.3x implied; Revenue ~SEK 70.6M (~A$10.6M est. from Swedish registry)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/apm/apm-human-services-international/news/apm-completes-ipo-acquisitions-and-amp-swedish-market-entry-2652618.html</t>
         </is>
       </c>
     </row>
@@ -1537,6 +1649,11 @@
           <t>ASX Announcement (Dec 2021); financial details not disclosed; described as not material to FY21 earnings</t>
         </is>
       </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-acquired-GMT-People-37179876/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1575,6 +1692,11 @@
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (Nov 2021); up to A$1.5M; revenue milestones A$12-16M; EBITDA not disclosed</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/hmi/hiremii-limited/news/acquisition-of-inverse-group-2625801.html</t>
         </is>
       </c>
     </row>
@@ -1615,6 +1737,11 @@
           <t>ASX Announcement (1 Jun 2021); A$6.7M upfront for 75% (up to A$10.5M for 100%); combined EBITDA with Techforce ~A$5.8M FY22; 14% revenue CAGR</t>
         </is>
       </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-completed-the-acquisition-of-75-majority-stake-in-Vision-Surveys-Pty-Ltd-36025964/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1657,6 +1784,11 @@
           <t>ASX Announcement (1 Jun 2021); A$23.8M for 79.3% (debt-free); expected FY22 EBITDA ~A$5.8M; ~4.1x implied</t>
         </is>
       </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-entered-into-binding-agreements-to-acquire-Techforce-Personnel-Pty-Ltd-for-35497394/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1697,6 +1829,11 @@
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (15 Mar 2021); A$3.1M cash; expected EBITDA A$1M in 12 months post-completion; ~3.1x implied</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-entered-into-a-binding-agreement-to-acquire-Business-of-SwingShift-Nurses-33481796/</t>
         </is>
       </c>
     </row>
@@ -1735,6 +1872,11 @@
           <t>ASX Announcement (19 Feb 2021); acquired via share swap (14.3M shares); EBITDA/Revenue not disclosed</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/hmi/hiremii-limited/news/hiremii-completes-acquisition-of-inverse-group-2635188.html</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1768,7 +1910,12 @@
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Feb 2021); financial details not publicly disclosed</t>
+          <t>ASX Announcement (Feb 2021); expected EBITDA A$1M; purchase price not separately disclosed</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.listcorp.com/asx/ppe/peoplein-limited/news/completion-of-swingshift-nurses-2525245.html</t>
         </is>
       </c>
     </row>
@@ -1811,6 +1958,11 @@
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M; ~4.0x implied</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-completed-the-acquisition-of-Ecareer-Employment-Services-Pty-Ltd-Illuminat-33544375/</t>
         </is>
       </c>
     </row>
@@ -1849,6 +2001,11 @@
           <t>ASX Announcement (15 Sep 2020); national rail training provider; financial terms not publicly disclosed</t>
         </is>
       </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://ashleyservicesgroup.com.au/ticrail-expands-into-western-australia/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1893,6 +2050,11 @@
           <t>ASX/media (Jun 2020); Serendipity (WA) = APM legal entity; MDP acquired 55% at ~A$1.5B EV from Quadrant PE; FY20 Revenue ~A$1.1B, EBITDA ~A$148M</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://michaelwest.com.au/apm-promoters-exit-jobless-profits-in-asx-float-turn-to-profiteering-from-disabled/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1935,6 +2097,11 @@
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (2019); A$11.2M for 80%; FY19 normalised EBITDA A$4.1M; Revenue A$40M</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lexology.com/library/detail.aspx?g=fe4a314d-4853-4892-83f1-ce9fb0ba5d5b</t>
         </is>
       </c>
     </row>
@@ -1977,6 +2144,11 @@
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (Jun 2019); A$16.8M combined with Carestaff; expected EBITDA A$3.4M combined</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fool.com.au/2019/06/19/people-infrastructure-announces-more-acquisitions/</t>
         </is>
       </c>
     </row>
@@ -2015,6 +2187,11 @@
           <t>ASX Announcement (Jun 2019); combined with First Choice Care (A$16.8M total); EBITDA A$3.4M combined; individual split not disclosed</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fool.com.au/2019/06/19/people-infrastructure-announces-more-acquisitions/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2055,6 +2232,11 @@
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (Jun 2019); A$13.5M upfront (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M; ~3.5x upfront</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessnewsaustralia.com/articles/people-infrastructure-buys-halcyon-knights-for--13-5m.html</t>
         </is>
       </c>
     </row>
@@ -2095,6 +2277,11 @@
           <t>ASX Announcement (Mar 2019); A$2.8M for remaining 50% shares; combined EBITDA with VNS ~A$1.1M incremental</t>
         </is>
       </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businessnewsaustralia.com/articles/steve-scanlan-sells-remaining-stake-in-recon-group.html</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2133,6 +2320,11 @@
           <t>ASX Announcement (Mar 2019); A$2.5M cash; combined EBITDA with Recon ~A$1.1M incremental; standalone EBITDA not disclosed</t>
         </is>
       </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finnewsnetwork.com.au/archives/finance_news_network222179.html</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2175,6 +2367,11 @@
           <t>ASX Announcement (Aug 2018); A$8M upfront (up to A$9.1M); EBITDA target ~A$2.65-2.8M; ~3.0x implied</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.staffingindustry.com/news/global-daily-news/australia-people-infrastructure-acquires-nursing-agency-business</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2215,6 +2412,11 @@
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months; ~3.5x stated</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.proactiveinvestors.com.au/companies/news/189851/people-infrastructure-s-acquisition-will-drive-revenue-higher-189851.html</t>
         </is>
       </c>
     </row>
@@ -2255,6 +2457,11 @@
           <t>MarketScreener; A$18.4M (A$16.6M cash + A$1.8M earnout); standalone EBITDA/Revenue not disclosed</t>
         </is>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/PEOPLEIN-LIMITED-38467017/news/People-Infrastructure-Ltd-acquired-AWX-Pty-Ltd-for-AUD-18-4-million-35119752/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ASX Scheme Booklet (Dec 2024); FY24 Operating EBITDA; EV includes ~$199M net debt</t>
+          <t>ASX Scheme Booklet (Dec 2024); FY24 Operating EBITDA (historical); 100% EV (equity + net corporate debt); fleet financing debt excluded</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (1 Mar 2024); ~A$9M base + ~A$1M earnout; 3.8-4.0x stated range</t>
+          <t>ASX Announcement (1 Mar 2024); ~A$9M base + ~A$1M earnout; 3.8-4.0x stated range; historical EBITDA; upfront CFDF basis</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="3" t="n">
-        <v>9.1</v>
+        <v>6.6</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>36.4</v>
+        <v>26.4</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (6 Nov 2023); A$26.4M upfront + A$9.9M deferred; ~4.0x upfront EV/EBITDA stated</t>
+          <t>ASX Announcement (6 Nov 2023); A$26.4M upfront + A$9.9M deferred (A$36.3M total); ~4.0x upfront EV/EBITDA stated; EBITDA back-solved from stated multiple; historical basis</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Jun 2022); A$17.6M upfront (up to A$23.5M with earnout); ~A$34M revenue, ~A$5M EBITDA</t>
+          <t>ASX Announcement (20 Jun 2022); A$17.6M upfront CFDF (up to A$23.5M with earnout); FY22 sustainable EBITDA ~A$5M (historical/normalised); asset acquisition</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Apr 2022); A$15M consideration; FY21 revenue ~$6.3M, EBITDA ~$3.8M</t>
+          <t>ASX Announcement (20 Apr 2022); A$15M total consideration; FY21 EBITDA ~$3.8M (historical)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (29 Jan 2020); 3.6x FY19 Operating EBITDA explicitly stated; A$62M cash + A$10M shares</t>
+          <t>ASX Announcement (29 Jan 2020); 3.6x FY19 Operating EBITDA explicitly stated (historical); A$62M cash + A$10M shares = A$72M total EV</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (17 Oct 2019); A$21.25M before earnouts; 4.4x FY19 normalised EBITDA stated</t>
+          <t>ASX Announcement (17 Oct 2019); A$21.25M upfront before earnouts; 4.4x FY19 normalised EBITDA stated (historical)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (30 Apr 2018); A$80M EV; ~3.3x annualised Operating EBITDA stated</t>
+          <t>ASX Announcement (30 Apr 2018); A$80M total EV; ~3.3x annualised Operating EBITDA stated (historical)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Feb 2026); NZD 24M upfront (NZD 56M max); NZD 5M EBITDA; 4.8x stated; converted at NZD/AUD ~0.92</t>
+          <t>ASX Announcement (20 Feb 2026); NZD 24M upfront CFDF (NZD 56M max); NZD 5M EBITDA (forward); 4.8x stated; converted at NZD/AUD ~0.92</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Dec 2025); A$20.25M; 6.2x FY25 earnings stated by PeopleIN</t>
+          <t>ASX Announcement (Dec 2025); A$20.25M total; 6.2x FY25 earnings stated by PeopleIN (historical)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ASX Scheme Booklet (Aug 2024); $1.45/share; ~A$1.3B equity + ~A$800M net debt; FY24 EBITDA A$281M</t>
+          <t>ASX Scheme Booklet (Aug 2024); $1.45/share; ~A$1.3B equity + ~A$800M net debt = ~A$2.1B 100% EV; FY24 Adjusted EBITDA A$281M (historical); scheme of arrangement</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (3 Feb 2023); A$14.2-15.9M; EBITDA A$4.1-5.0M expected FY23; Revenue ~A$62.8M (FY24 full year)</t>
+          <t>ASX Announcement (3 Feb 2023); A$14.2-15.9M range (midpoint used); EBITDA A$4.1-5.0M expected FY23 (forward); Revenue ~A$62.8M</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Nov 2022); A$239.8M (US$153.5M); FY22 Revenue A$454.7M, EBITDA A$50M</t>
+          <t>ASX Announcement (Nov 2022); A$239.8M (US$153.5M) total EV; FY22 EBITDA A$50M (historical)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1453,14 +1453,14 @@
         <v>1.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (30 May 2022); A$3.6-4.2M for 75%; normalised FY22 EBITDA A$1.4M; Revenue ~A$14M</t>
+          <t>ASX Announcement (30 May 2022); A$4.2M for 75% (implied 100% EV A$5.6M); normalised FY22 EBITDA A$1.4M (100% basis); historical</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (3 Jun 2022); A$45M upfront (A$70M max); expected FY23 EBITDA ~A$9.5M; 4.7x upfront; Revenue ~A$60M (est.)</t>
+          <t>ASX Announcement (3 Jun 2022); A$45M upfront CFDF (A$70M max with earnout); expected FY23 EBITDA ~A$9.5M (forward); 4.7x upfront</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (9 Feb 2022); A$16M upfront (up to A$26.8M); expected FY23 EBITDA ~A$4.3M</t>
+          <t>ASX Announcement (9 Feb 2022); A$16M upfront CFDF (up to A$26.8M); expected FY23 EBITDA ~A$4.3M (forward); 3.7x upfront</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M); expected FY22 EBITDA SEK 12M (~A$2M); ~8.3x implied; Revenue ~SEK 70.6M (~A$10.6M est. from Swedish registry)</t>
+          <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M) total; expected FY22 EBITDA SEK 12M (~A$2M) (forward); ~8.3x implied</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1774,14 +1774,14 @@
         <v>5.8</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>23.8</v>
+        <v>30</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (1 Jun 2021); A$23.8M for 79.3% (debt-free); expected FY22 EBITDA ~A$5.8M; ~4.1x implied</t>
+          <t>ASX Announcement (1 Jun 2021); A$23.8M for 79.3% debt-free (implied 100% EV A$30.0M); expected FY22 EBITDA ~A$5.8M (100% basis); forward</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (15 Mar 2021); A$3.1M cash; expected EBITDA A$1M in 12 months post-completion; ~3.1x implied</t>
+          <t>ASX Announcement (15 Mar 2021); A$3.1M cash upfront; expected EBITDA A$1M over next 12 months (forward); ~3.1x implied</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M; ~4.0x implied</t>
+          <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M (forward); ~4.0x implied</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>ASX/media (Jun 2020); Serendipity (WA) = APM legal entity; MDP acquired 55% at ~A$1.5B EV from Quadrant PE; FY20 Revenue ~A$1.1B, EBITDA ~A$148M</t>
+          <t>Media reports (Jun 2020); Serendipity (WA) = APM legal entity; MDP acquired 55% at ~A$1.5-1.6B implied 100% EV from Quadrant PE; FY20 EBITDA ~A$148M (historical)</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2089,14 +2089,14 @@
         <v>4.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>11.2</v>
+        <v>14</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (2019); A$11.2M for 80%; FY19 normalised EBITDA A$4.1M; Revenue A$40M</t>
+          <t>ASX Announcement (2019); A$11.2M for 80% (implied 100% EV A$14.0M); FY19 normalised EBITDA A$4.1M (100% basis); historical</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); A$16.8M combined with Carestaff; expected EBITDA A$3.4M combined</t>
+          <t>ASX Announcement (Jun 2019); A$16.8M combined upfront with Carestaff; expected FY20 EBITDA A$3.4M combined (forward)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); A$13.5M upfront (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M; ~3.5x upfront</t>
+          <t>ASX Announcement (Jun 2019); A$13.5M upfront CFDF (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M (forward); ~3.5x upfront</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Aug 2018); A$8M upfront (up to A$9.1M); EBITDA target ~A$2.65-2.8M; ~3.0x implied</t>
+          <t>ASX Announcement (Aug 2018); A$8M upfront (up to A$9.1M); FY19 EBITDA target ~A$2.65-2.8M (forward); ~3.0x upfront implied</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months; ~3.5x stated</t>
+          <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months (forward); ~3.5x explicitly stated; consistent on 50% or 100% basis</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="34">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">

--- a/Comparable_Transaction_Analysis.xlsx
+++ b/Comparable_Transaction_Analysis.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ASX Scheme Booklet (Dec 2024); FY24 Operating EBITDA (historical); 100% EV (equity + net corporate debt); fleet financing debt excluded</t>
+          <t>ASX Scheme Booklet (Dec 2024); FY24 Operating EBITDA A$171M (historical); 100% EV (equity + net corporate debt); 8.2x implied; fleet financing debt excluded</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -627,14 +627,14 @@
         <v>2.4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (1 Mar 2024); ~A$9M base + ~A$1M earnout; 3.8-4.0x stated range; historical EBITDA; upfront CFDF basis</t>
+          <t>ASX Announcement (1 Mar 2024); A$9M base + up to A$1M earnout; EBITDA A$2.4M annualised (run-rate); ~3.8x on base (FY24 annual report cites 3.8-4.0x range for ACF acquisitions); multiple implied</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (6 Nov 2023); A$26.4M upfront + A$9.9M deferred (A$36.3M total); ~4.0x upfront EV/EBITDA stated; EBITDA back-solved from stated multiple; historical basis</t>
+          <t>ASX Announcement (6 Nov 2023); A$26.4M upfront CFDF + A$9.9M deferred (A$36.3M total); "about 4.0x" upfront EV/EBITDA explicitly stated; EBITDA ~A$6.6M back-solved; historical</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Jun 2022); A$17.6M upfront CFDF (up to A$23.5M with earnout); FY22 sustainable EBITDA ~A$5M (historical/normalised); asset acquisition</t>
+          <t>ASX Announcement (20 Jun 2022); A$17.6M upfront CFDF (up to A$23.5M with earnout); FY22 sustainable EBITDA ~A$5M (historical); 3.5x implied; asset acquisition</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Apr 2022); A$15M total consideration; FY21 EBITDA ~$3.8M (historical)</t>
+          <t>ASX Announcement (20 Apr 2022); A$15M total consideration; FY21 EBITDA ~A$3.8M (historical); 3.9x implied</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (29 Jan 2020); 3.6x FY19 Operating EBITDA explicitly stated (historical); A$62M cash + A$10M shares = A$72M total EV</t>
+          <t>ASX Announcement (29 Jan 2020); 3.6x FY19 Operating EBITDA explicitly stated (historical); A$62M cash + A$10M shares = A$72M EV CFDF</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (30 Apr 2018); A$80M total EV; ~3.3x annualised Operating EBITDA stated (historical)</t>
+          <t>ASX Announcement (30 Apr 2018); A$80M total EV; "circa 3.3x" annualised March quarter Operating EBITDA explicitly stated (run-rate); A$24.2M EBITDA back-solved</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="15">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (20 Feb 2026); NZD 24M upfront CFDF (NZD 56M max); NZD 5M EBITDA (forward); 4.8x stated; converted at NZD/AUD ~0.92</t>
+          <t>ASX Announcement (20 Feb 2026); NZD 24M upfront (NZD 56M max); NZD 5M EBITDA (forward); 4.8x explicitly stated; converted at NZD/AUD ~0.92</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Dec 2025); A$20.25M total; 6.2x FY25 earnings stated by PeopleIN (historical)</t>
+          <t>ASX Announcement (Dec 2025); A$20.25M total; 6.2x FY25 earnings explicitly stated by PeopleIN (historical)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ASX Scheme Booklet (Aug 2024); $1.45/share; ~A$1.3B equity + ~A$800M net debt = ~A$2.1B 100% EV; FY24 Adjusted EBITDA A$281M (historical); scheme of arrangement</t>
+          <t>ASX Scheme Booklet (Aug 2024); $1.45/share; ~A$1.3B equity + net debt; FY24 Underlying EBITDA ~A$280M (historical); 7.5x implied; NOTE: some data providers show EV ~A$2.27B / ~8.1x depending on net debt definition</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (3 Feb 2023); A$14.2-15.9M range (midpoint used); EBITDA A$4.1-5.0M expected FY23 (forward); Revenue ~A$62.8M</t>
+          <t>ASX Announcement (3 Feb 2023); A$14.2-15.9M range (midpoint used); EBITDA A$4.1-5.0M expected FY23 (forward); 3.4x implied from midpoints</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Nov 2022); A$239.8M (US$153.5M) total EV; FY22 EBITDA A$50M (historical)</t>
+          <t>ASX Announcement (Nov 2022); A$239.8M (US$153.5M) CFDF; FY22 Underlying EBITDA A$50M (historical); 4.8x implied</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (30 May 2022); A$4.2M for 75% (implied 100% EV A$5.6M); normalised FY22 EBITDA A$1.4M (100% basis); historical</t>
+          <t>ASX Announcement (30 May 2022); A$4.2M for 75% (implied 100% EV A$5.6M); normalised FY22 EBITDA A$1.4M (100% basis); historical; 4.0x implied</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (3 Jun 2022); A$45M upfront CFDF (A$70M max with earnout); expected FY23 EBITDA ~A$9.5M (forward); 4.7x upfront</t>
+          <t>ASX Announcement (3 Jun 2022); A$45M upfront CFDF (A$70M max); expected FY23 EBITDA ~A$9.5M (forward); 4.7x explicitly stated</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (9 Feb 2022); A$16M upfront CFDF (up to A$26.8M); expected FY23 EBITDA ~A$4.3M (forward); 3.7x upfront</t>
+          <t>ASX Announcement (9 Feb 2022); A$16M upfront CFDF (up to A$26.8M); expected FY23 EBITDA ~A$4.3M (forward); 3.7x implied</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M) total; expected FY22 EBITDA SEK 12M (~A$2M) (forward); ~8.3x implied</t>
+          <t>ASX Announcement (29 Dec 2021); SEK 100M (~A$15M) total; expected FY22 EBITDA SEK 12M (~A$2M) (forward); 8.3x implied</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (1 Jun 2021); A$23.8M for 79.3% debt-free (implied 100% EV A$30.0M); expected FY22 EBITDA ~A$5.8M (100% basis); forward</t>
+          <t>ASX Announcement (1 Jun 2021); A$23.8M for 79.3% debt-free (implied 100% EV A$30.0M); expected FY22 EBITDA ~A$5.8M (100% basis); forward; 5.2x implied</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (15 Mar 2021); A$3.1M cash upfront; expected EBITDA A$1M over next 12 months (forward); ~3.1x implied</t>
+          <t>ASX Announcement (15 Mar 2021); A$3.1M cash upfront; expected EBITDA A$1M over next 12 months (forward); 3.1x implied</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (19 Feb 2021); acquired via share swap (14.3M shares); EBITDA/Revenue not disclosed</t>
+          <t>⚠ NO ASX SOURCE (pre-IPO scrip deal, ~A$2.85M implied at IPO price); EBITDA/Revenue not disclosed</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M (forward); ~4.0x implied</t>
+          <t>ASX Announcement (17 Dec 2020); A$5.15M (~A$5.2M net of cash); expected EBITDA A$1.3M (forward); 4.0x implied</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Media reports (Jun 2020); Serendipity (WA) = APM legal entity; MDP acquired 55% at ~A$1.5-1.6B implied 100% EV from Quadrant PE; FY20 EBITDA ~A$148M (historical)</t>
+          <t>⚠ NO ASX SOURCE (APM was private; IPO Nov 2021). Media/IPO prospectus only; MDP acquired 55% at ~A$1.5B implied 100% EV from Quadrant PE; FY20 EBITDA A$148.4M (historical); 10.1x implied</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (2019); A$11.2M for 80% (implied 100% EV A$14.0M); FY19 normalised EBITDA A$4.1M (100% basis); historical</t>
+          <t>ASX Announcement (Aug 2019); A$11.2M for 80% (implied 100% EV A$14.0M); FY19 normalised EBITDA A$4.1M (100% basis); historical; 3.4x implied</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); A$16.8M combined upfront with Carestaff; expected FY20 EBITDA A$3.4M combined (forward)</t>
+          <t>ASX Announcement (Jun 2019); A$16.8M combined upfront with Carestaff (no earnout); expected FY20 EBITDA A$3.4M combined (forward); 4.9x implied</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jun 2019); A$13.5M upfront CFDF (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M (forward); ~3.5x upfront</t>
+          <t>ASX Announcement (Jun 2019); A$13.5M upfront (up to A$21.75M with earnout); expected FY20 EBITDA A$3.9M (forward); 3.5x implied</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Aug 2018); A$8M upfront (up to A$9.1M); FY19 EBITDA target ~A$2.65-2.8M (forward); ~3.0x upfront implied</t>
+          <t>ASX Announcement (Aug 2018); A$8M upfront (up to A$9.1M); FY19 EBITDA target ~A$2.65-2.8M (forward, midpoint used); 3.0x implied</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months (forward); ~3.5x explicitly stated; consistent on 50% or 100% basis</t>
+          <t>ASX Announcement (Jan 2018); A$2.8M for 50% stake; expected A$0.8M EBITDA (50% share) over 12 months (forward); 3.5x explicitly stated; consistent on 50% or 100% basis</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
